--- a/graduacion/graduacion.xlsx
+++ b/graduacion/graduacion.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/graduacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5578A9E1-6650-8249-B298-41244233082C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B5F17A-C24C-DD4B-813E-9A534697B973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="2000" windowWidth="24460" windowHeight="14820" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="43">
   <si>
-    <t>Avance al 25 de febrero de 2026.</t>
-  </si>
-  <si>
     <t>PÓLIZAS</t>
   </si>
   <si>
@@ -165,6 +162,9 @@
   </si>
   <si>
     <t>TOTAL2</t>
+  </si>
+  <si>
+    <t>Avance al 28 de febrero de 2026.</t>
   </si>
 </sst>
 </file>
@@ -173,10 +173,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yy;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -277,7 +277,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -286,10 +286,10 @@
     <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -301,7 +301,7 @@
     <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -316,19 +316,19 @@
     <xf numFmtId="17" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -340,13 +340,13 @@
     <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -364,16 +364,16 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -390,10 +390,758 @@
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
-    <dxf>
-      <font>
-        <b/>
+  <dxfs count="59">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="16"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="31"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="16"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="31"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -404,6 +1152,455 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
+        <name val="Cambria"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -416,781 +1613,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="centerContinuous" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Cambria"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="#,##0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="#,##0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="#,##0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="16"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="31"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1206,32 +1628,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W14" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W14" totalsRowShown="0" headerRowDxfId="58">
   <autoFilter ref="A3:W14" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}"/>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="15" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="14" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="13" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="12" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="11" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="10"/>
-    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="9"/>
-    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="8"/>
-    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="7"/>
-    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="6"/>
-    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="5"/>
-    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="4"/>
-    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="3"/>
-    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="2"/>
-    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="49" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="48" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="47" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="46" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="45" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="44"/>
+    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="43"/>
+    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="42"/>
+    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="41"/>
+    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="40"/>
+    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="39"/>
+    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="38"/>
+    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="37"/>
+    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="36"/>
+    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1572,7 +1994,7 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1613,88 +2035,88 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="12" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="12"/>
       <c r="Q2" s="12"/>
       <c r="R2" s="12"/>
       <c r="S2" s="13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" s="13"/>
       <c r="U2" s="13"/>
       <c r="V2" s="2"/>
       <c r="W2" s="10"/>
     </row>
-    <row r="3" spans="1:23" ht="42" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="D3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="H3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="I3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="J3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="K3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="L3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="M3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="N3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="O3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="P3" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="18" t="s">
+      <c r="Q3" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="18" t="s">
+      <c r="R3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="R3" s="18" t="s">
+      <c r="S3" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="S3" s="13" t="s">
+      <c r="T3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="T3" s="13" t="s">
+      <c r="U3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="V3" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="U3" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="V3" s="19" t="s">
+      <c r="W3" s="19" t="s">
         <v>23</v>
-      </c>
-      <c r="W3" s="19" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
@@ -1724,13 +2146,13 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="C5" s="30" t="s">
         <v>26</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>27</v>
       </c>
       <c r="D5" s="10">
         <v>2043</v>
@@ -1739,13 +2161,13 @@
         <v>2856</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" s="10">
         <v>111960</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I5" s="31">
         <v>13</v>
@@ -1760,10 +2182,10 @@
         <v>46023</v>
       </c>
       <c r="M5" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="10" t="s">
         <v>30</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>31</v>
       </c>
       <c r="O5" s="34">
         <v>11.5</v>
@@ -1791,13 +2213,13 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="C6" s="30" t="s">
         <v>26</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>27</v>
       </c>
       <c r="D6" s="10">
         <v>2043</v>
@@ -1806,13 +2228,13 @@
         <v>2856</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="10">
         <v>112522</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6" s="31">
         <v>11</v>
@@ -1827,10 +2249,10 @@
         <v>46082</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O6" s="34">
         <v>6</v>
@@ -1858,13 +2280,13 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="C7" s="30" t="s">
         <v>26</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>27</v>
       </c>
       <c r="D7" s="10">
         <v>2043</v>
@@ -1873,13 +2295,13 @@
         <v>2043</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="10">
         <v>113076</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I7" s="31">
         <v>10</v>
@@ -1894,10 +2316,10 @@
         <v>46113</v>
       </c>
       <c r="M7" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O7" s="34">
         <v>10.5</v>
@@ -1912,26 +2334,26 @@
         <v>0</v>
       </c>
       <c r="S7" s="37">
-        <v>60761.25</v>
+        <v>63457.279999999999</v>
       </c>
       <c r="T7" s="37">
         <v>35462.339999999997</v>
       </c>
       <c r="U7" s="38">
-        <v>96223.59</v>
+        <v>98919.62</v>
       </c>
       <c r="V7" s="20"/>
       <c r="W7" s="39"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="C8" s="30" t="s">
         <v>26</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>27</v>
       </c>
       <c r="D8" s="10">
         <v>2043</v>
@@ -1940,13 +2362,13 @@
         <v>2856</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" s="10">
         <v>114100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I8" s="31">
         <v>8</v>
@@ -1961,10 +2383,10 @@
         <v>46174</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O8" s="34">
         <v>13.5</v>
@@ -1979,26 +2401,26 @@
         <v>0</v>
       </c>
       <c r="S8" s="37">
-        <v>69147.08</v>
+        <v>69864.42</v>
       </c>
       <c r="T8" s="37">
         <v>492.87</v>
       </c>
       <c r="U8" s="38">
-        <v>69639.95</v>
+        <v>70357.289999999994</v>
       </c>
       <c r="V8" s="20"/>
       <c r="W8" s="39"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="C9" s="30" t="s">
         <v>26</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>27</v>
       </c>
       <c r="D9" s="10">
         <v>2043</v>
@@ -2007,13 +2429,13 @@
         <v>2692</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9" s="10">
         <v>113450</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I9" s="31">
         <v>8</v>
@@ -2028,10 +2450,10 @@
         <v>46174</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O9" s="34">
         <v>11.5</v>
@@ -2046,26 +2468,26 @@
         <v>0</v>
       </c>
       <c r="S9" s="37">
-        <v>75546</v>
+        <v>82418.039999999994</v>
       </c>
       <c r="T9" s="37">
         <v>17462.349999999999</v>
       </c>
       <c r="U9" s="38">
-        <v>93008.35</v>
+        <v>99880.39</v>
       </c>
       <c r="V9" s="20"/>
       <c r="W9" s="39"/>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="C10" s="30" t="s">
         <v>26</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>27</v>
       </c>
       <c r="D10" s="10">
         <v>2043</v>
@@ -2074,13 +2496,13 @@
         <v>2692</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10" s="10">
         <v>114431</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I10" s="31">
         <v>6</v>
@@ -2095,10 +2517,10 @@
         <v>46235</v>
       </c>
       <c r="M10" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O10" s="34">
         <v>6.5</v>
@@ -2113,26 +2535,26 @@
         <v>0</v>
       </c>
       <c r="S10" s="37">
-        <v>22578.06</v>
+        <v>23170.33</v>
       </c>
       <c r="T10" s="37">
         <v>2343.7399999999998</v>
       </c>
       <c r="U10" s="38">
-        <v>24921.8</v>
+        <v>25514.07</v>
       </c>
       <c r="V10" s="20"/>
       <c r="W10" s="39"/>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="C11" s="30" t="s">
         <v>26</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>27</v>
       </c>
       <c r="D11" s="10">
         <v>2043</v>
@@ -2141,13 +2563,13 @@
         <v>2692</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" s="10">
         <v>114157</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I11" s="31">
         <v>6</v>
@@ -2162,10 +2584,10 @@
         <v>46235</v>
       </c>
       <c r="M11" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O11" s="34">
         <v>8</v>
@@ -2193,13 +2615,13 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="C12" s="30" t="s">
         <v>26</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>27</v>
       </c>
       <c r="D12" s="10">
         <v>2043</v>
@@ -2208,13 +2630,13 @@
         <v>2856</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" s="10">
         <v>115047</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I12" s="31">
         <v>5</v>
@@ -2229,10 +2651,10 @@
         <v>46266</v>
       </c>
       <c r="M12" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O12" s="34">
         <v>13.5</v>
@@ -2247,26 +2669,26 @@
         <v>0</v>
       </c>
       <c r="S12" s="37">
-        <v>76912.52</v>
+        <v>78451.61</v>
       </c>
       <c r="T12" s="37">
         <v>8793.7800000000007</v>
       </c>
       <c r="U12" s="38">
-        <v>85706.3</v>
+        <v>87245.39</v>
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="39"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="C13" s="30" t="s">
         <v>26</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>27</v>
       </c>
       <c r="D13" s="10">
         <v>2043</v>
@@ -2275,13 +2697,13 @@
         <v>2043</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13" s="10">
         <v>115404</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I13" s="31">
         <v>4</v>
@@ -2296,44 +2718,44 @@
         <v>46296</v>
       </c>
       <c r="M13" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O13" s="34">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="P13" s="35">
         <v>0</v>
       </c>
       <c r="Q13" s="36">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="R13" s="36">
         <v>0</v>
       </c>
       <c r="S13" s="37">
-        <v>51028.32</v>
+        <v>51820.11</v>
       </c>
       <c r="T13" s="37">
-        <v>6781.19</v>
+        <v>7384.25</v>
       </c>
       <c r="U13" s="38">
-        <v>57809.51</v>
+        <v>59204.36</v>
       </c>
       <c r="V13" s="20"/>
       <c r="W13" s="39"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="C14" s="30" t="s">
         <v>26</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>27</v>
       </c>
       <c r="D14" s="10">
         <v>2043</v>
@@ -2342,13 +2764,13 @@
         <v>2856</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G14" s="10">
         <v>116060</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I14" s="31">
         <v>3</v>
@@ -2363,10 +2785,10 @@
         <v>46327</v>
       </c>
       <c r="M14" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O14" s="34">
         <v>8.5</v>
@@ -2381,85 +2803,125 @@
         <v>0</v>
       </c>
       <c r="S14" s="37">
-        <v>35248.300000000003</v>
+        <v>35767.94</v>
       </c>
       <c r="T14" s="37">
         <v>3198.71</v>
       </c>
       <c r="U14" s="38">
-        <v>38447.01</v>
+        <v>38966.65</v>
       </c>
       <c r="V14" s="20"/>
       <c r="W14" s="39"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="V5:V14">
-    <cfRule type="cellIs" dxfId="38" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:R14 N5:N14">
-    <cfRule type="expression" dxfId="36" priority="23">
+    <cfRule type="expression" dxfId="20" priority="23">
       <formula>AND($B5&lt;&gt;"",$O5&lt;&gt;"2",,$O5&lt;&gt;"3")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="35" priority="19">
+    <cfRule type="expression" dxfId="19" priority="19">
       <formula>"y($B18&lt;&gt;"",r18&lt;36)"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q14">
-    <cfRule type="expression" dxfId="34" priority="18">
+  <conditionalFormatting sqref="Q5:Q9">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U14">
-    <cfRule type="expression" dxfId="33" priority="17">
+  <conditionalFormatting sqref="U5:U9">
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:W14">
-    <cfRule type="expression" dxfId="32" priority="22">
+    <cfRule type="expression" dxfId="16" priority="22">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:W14">
-    <cfRule type="expression" dxfId="31" priority="12">
+    <cfRule type="expression" dxfId="15" priority="12">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q5:Q14">
+    <cfRule type="expression" dxfId="14" priority="11">
+      <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="R5:R14">
-    <cfRule type="expression" dxfId="30" priority="15">
+    <cfRule type="expression" dxfId="13" priority="15">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="U5:U14">
+    <cfRule type="expression" dxfId="12" priority="16">
+      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="V5:V14">
-    <cfRule type="cellIs" dxfId="29" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:W14">
-    <cfRule type="containsText" dxfId="27" priority="10" operator="containsText" text="No cumple">
+    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="No cumple">
       <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:W14">
+    <cfRule type="expression" dxfId="8" priority="5">
+      <formula>$B5&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q5:Q14">
+    <cfRule type="expression" dxfId="7" priority="4">
+      <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:R14">
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U5:U14">
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="V5:V14">
-    <cfRule type="cellIs" dxfId="26" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:W14">
-    <cfRule type="containsText" dxfId="24" priority="3" operator="containsText" text="No cumple">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="No cumple">
       <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q10:Q14">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND($B10&lt;&gt;"",Q10&lt;36)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U10:U14">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND($B10&lt;&gt;"",U10&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/graduacion/graduacion.xlsx
+++ b/graduacion/graduacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/graduacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B5F17A-C24C-DD4B-813E-9A534697B973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC20918-6AAA-4245-A009-7622FAA53417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="2000" windowWidth="24460" windowHeight="14820" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
     <t>TOTAL2</t>
   </si>
   <si>
-    <t>Avance al 28 de febrero de 2026.</t>
+    <t>Avance al 11 de marzo de 2026.</t>
   </si>
 </sst>
 </file>
@@ -390,47 +390,7 @@
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="59">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="39">
     <dxf>
       <font>
         <b/>
@@ -496,8 +456,24 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <border>
         <left style="hair">
           <color indexed="64"/>
@@ -517,10 +493,15 @@
       <font>
         <b/>
         <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <border>
         <left style="hair">
           <color indexed="64"/>
@@ -540,7 +521,9 @@
       <font>
         <b/>
         <i val="0"/>
-        <color rgb="FFFF0000"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
       </font>
       <border>
         <left style="hair">
@@ -574,11 +557,109 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="16"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="31"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -633,509 +714,6 @@
         </top>
         <bottom style="hair">
           <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="16"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="31"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="16"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="31"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
         </bottom>
       </border>
     </dxf>
@@ -1628,32 +1206,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W14" totalsRowShown="0" headerRowDxfId="58">
-  <autoFilter ref="A3:W14" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W15" totalsRowShown="0" headerRowDxfId="38">
+  <autoFilter ref="A3:W15" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}"/>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="49" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="48" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="47" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="46" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="45" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="44"/>
-    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="43"/>
-    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="42"/>
-    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="41"/>
-    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="40"/>
-    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="39"/>
-    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="38"/>
-    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="37"/>
-    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="36"/>
-    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="29" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="28" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="27" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="26" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="25" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="24"/>
+    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="23"/>
+    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="22"/>
+    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="21"/>
+    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="20"/>
+    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="19"/>
+    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="18"/>
+    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="17"/>
+    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="16"/>
+    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1976,7 +1554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52C454C9-C0D9-734E-BED4-594891A853F9}">
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
@@ -2170,7 +1748,7 @@
         <v>28</v>
       </c>
       <c r="I5" s="31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J5" s="32">
         <v>45707</v>
@@ -2237,7 +1815,7 @@
         <v>31</v>
       </c>
       <c r="I6" s="31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6" s="32">
         <v>45776</v>
@@ -2304,7 +1882,7 @@
         <v>33</v>
       </c>
       <c r="I7" s="31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7" s="32">
         <v>45806</v>
@@ -2371,7 +1949,7 @@
         <v>34</v>
       </c>
       <c r="I8" s="31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J8" s="32">
         <v>45863</v>
@@ -2438,7 +2016,7 @@
         <v>35</v>
       </c>
       <c r="I9" s="31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" s="32">
         <v>45852</v>
@@ -2468,13 +2046,13 @@
         <v>0</v>
       </c>
       <c r="S9" s="37">
-        <v>82418.039999999994</v>
+        <v>77467.86</v>
       </c>
       <c r="T9" s="37">
         <v>17462.349999999999</v>
       </c>
       <c r="U9" s="38">
-        <v>99880.39</v>
+        <v>94930.21</v>
       </c>
       <c r="V9" s="20"/>
       <c r="W9" s="39"/>
@@ -2505,7 +2083,7 @@
         <v>36</v>
       </c>
       <c r="I10" s="31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J10" s="32">
         <v>45930</v>
@@ -2572,7 +2150,7 @@
         <v>37</v>
       </c>
       <c r="I11" s="31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" s="32">
         <v>45904</v>
@@ -2602,13 +2180,13 @@
         <v>0</v>
       </c>
       <c r="S11" s="37">
-        <v>24689.040000000001</v>
+        <v>26317.68</v>
       </c>
       <c r="T11" s="37">
         <v>7460.28</v>
       </c>
       <c r="U11" s="38">
-        <v>32149.32</v>
+        <v>33777.96</v>
       </c>
       <c r="V11" s="20"/>
       <c r="W11" s="39"/>
@@ -2639,7 +2217,7 @@
         <v>38</v>
       </c>
       <c r="I12" s="31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" s="32">
         <v>45944</v>
@@ -2669,13 +2247,13 @@
         <v>0</v>
       </c>
       <c r="S12" s="37">
-        <v>78451.61</v>
+        <v>83519.55</v>
       </c>
       <c r="T12" s="37">
         <v>8793.7800000000007</v>
       </c>
       <c r="U12" s="38">
-        <v>87245.39</v>
+        <v>92313.33</v>
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="39"/>
@@ -2706,7 +2284,7 @@
         <v>39</v>
       </c>
       <c r="I13" s="31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J13" s="32">
         <v>45986</v>
@@ -2773,7 +2351,7 @@
         <v>40</v>
       </c>
       <c r="I14" s="31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="32">
         <v>46010</v>
@@ -2803,125 +2381,110 @@
         <v>0</v>
       </c>
       <c r="S14" s="37">
-        <v>35767.94</v>
+        <v>36877</v>
       </c>
       <c r="T14" s="37">
         <v>3198.71</v>
       </c>
       <c r="U14" s="38">
-        <v>38966.65</v>
+        <v>40075.71</v>
       </c>
       <c r="V14" s="20"/>
       <c r="W14" s="39"/>
     </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="28"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="26"/>
+      <c r="W15" s="29"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="V5:V14">
-    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="20" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="21" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:R14 N5:N14">
-    <cfRule type="expression" dxfId="20" priority="23">
+    <cfRule type="expression" dxfId="12" priority="23">
       <formula>AND($B5&lt;&gt;"",$O5&lt;&gt;"2",,$O5&lt;&gt;"3")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="19" priority="19">
+    <cfRule type="expression" dxfId="11" priority="19">
       <formula>"y($B18&lt;&gt;"",r18&lt;36)"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="18" priority="18">
+  <conditionalFormatting sqref="Q5:Q14">
+    <cfRule type="expression" dxfId="10" priority="18">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U9">
-    <cfRule type="expression" dxfId="17" priority="17">
+  <conditionalFormatting sqref="U5:U14">
+    <cfRule type="expression" dxfId="9" priority="17">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:W14">
-    <cfRule type="expression" dxfId="16" priority="22">
+    <cfRule type="expression" dxfId="8" priority="22">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:W14">
-    <cfRule type="expression" dxfId="15" priority="12">
+    <cfRule type="expression" dxfId="7" priority="12">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q14">
-    <cfRule type="expression" dxfId="14" priority="11">
-      <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="R5:R14">
-    <cfRule type="expression" dxfId="13" priority="15">
+    <cfRule type="expression" dxfId="6" priority="15">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U14">
-    <cfRule type="expression" dxfId="12" priority="16">
-      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="V5:V14">
-    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="13" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="14" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:W14">
-    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="No cumple">
+    <cfRule type="containsText" dxfId="3" priority="10" operator="containsText" text="No cumple">
       <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W14">
-    <cfRule type="expression" dxfId="8" priority="5">
-      <formula>$B5&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q14">
-    <cfRule type="expression" dxfId="7" priority="4">
-      <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R14">
-    <cfRule type="expression" dxfId="6" priority="8">
-      <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U14">
-    <cfRule type="expression" dxfId="5" priority="9">
-      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="V5:V14">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:W14">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="No cumple">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="No cumple">
       <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q10:Q14">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND($B10&lt;&gt;"",Q10&lt;36)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U10:U14">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND($B10&lt;&gt;"",U10&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/graduacion/graduacion.xlsx
+++ b/graduacion/graduacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/graduacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC20918-6AAA-4245-A009-7622FAA53417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D09B9A5-3944-9742-AB06-23F4420B783A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16360" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
     <t>TOTAL2</t>
   </si>
   <si>
-    <t>Avance al 11 de marzo de 2026.</t>
+    <t>Avance al 13 de marzo de 2026.</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,47 @@
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="59">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -456,6 +496,85 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <color rgb="FFC00000"/>
@@ -519,11 +638,51 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
       </font>
       <border>
         <left style="hair">
@@ -714,6 +873,269 @@
         </top>
         <bottom style="hair">
           <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="16"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="31"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
         </bottom>
       </border>
     </dxf>
@@ -1206,32 +1628,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W15" totalsRowShown="0" headerRowDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W15" totalsRowShown="0" headerRowDxfId="58">
   <autoFilter ref="A3:W15" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}"/>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="29" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="28" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="27" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="26" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="25" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="24"/>
-    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="23"/>
-    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="22"/>
-    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="21"/>
-    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="20"/>
-    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="19"/>
-    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="18"/>
-    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="17"/>
-    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="16"/>
-    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="49" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="48" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="47" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="46" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="45" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="44"/>
+    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="43"/>
+    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="42"/>
+    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="41"/>
+    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="40"/>
+    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="39"/>
+    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="38"/>
+    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="37"/>
+    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="36"/>
+    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1979,13 +2401,13 @@
         <v>0</v>
       </c>
       <c r="S8" s="37">
-        <v>69864.42</v>
+        <v>70195.740000000005</v>
       </c>
       <c r="T8" s="37">
         <v>492.87</v>
       </c>
       <c r="U8" s="38">
-        <v>70357.289999999994</v>
+        <v>70688.61</v>
       </c>
       <c r="V8" s="20"/>
       <c r="W8" s="39"/>
@@ -2180,13 +2602,13 @@
         <v>0</v>
       </c>
       <c r="S11" s="37">
-        <v>26317.68</v>
+        <v>26906.37</v>
       </c>
       <c r="T11" s="37">
         <v>7460.28</v>
       </c>
       <c r="U11" s="38">
-        <v>33777.96</v>
+        <v>34366.65</v>
       </c>
       <c r="V11" s="20"/>
       <c r="W11" s="39"/>
@@ -2419,72 +2841,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="V5:V14">
-    <cfRule type="cellIs" dxfId="14" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:R14 N5:N14">
-    <cfRule type="expression" dxfId="12" priority="23">
+    <cfRule type="expression" dxfId="20" priority="23">
       <formula>AND($B5&lt;&gt;"",$O5&lt;&gt;"2",,$O5&lt;&gt;"3")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="11" priority="19">
+    <cfRule type="expression" dxfId="19" priority="19">
       <formula>"y($B18&lt;&gt;"",r18&lt;36)"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q14">
-    <cfRule type="expression" dxfId="10" priority="18">
+  <conditionalFormatting sqref="Q5:Q9">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U14">
-    <cfRule type="expression" dxfId="9" priority="17">
+  <conditionalFormatting sqref="U5:U9">
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:W14">
-    <cfRule type="expression" dxfId="8" priority="22">
+    <cfRule type="expression" dxfId="16" priority="22">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:W14">
-    <cfRule type="expression" dxfId="7" priority="12">
+    <cfRule type="expression" dxfId="15" priority="12">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q5:Q14">
+    <cfRule type="expression" dxfId="14" priority="11">
+      <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="R5:R14">
-    <cfRule type="expression" dxfId="6" priority="15">
+    <cfRule type="expression" dxfId="13" priority="15">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="U5:U14">
+    <cfRule type="expression" dxfId="12" priority="16">
+      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="V5:V14">
-    <cfRule type="cellIs" dxfId="5" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:W14">
-    <cfRule type="containsText" dxfId="3" priority="10" operator="containsText" text="No cumple">
+    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="No cumple">
       <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:W14">
+    <cfRule type="expression" dxfId="8" priority="5">
+      <formula>$B5&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q5:Q14">
+    <cfRule type="expression" dxfId="7" priority="4">
+      <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:R14">
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U5:U14">
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="V5:V14">
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:W14">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="No cumple">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="No cumple">
       <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q10:Q14">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND($B10&lt;&gt;"",Q10&lt;36)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U10:U14">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND($B10&lt;&gt;"",U10&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/graduacion/graduacion.xlsx
+++ b/graduacion/graduacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/graduacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D09B9A5-3944-9742-AB06-23F4420B783A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89D1F8C-3D05-3E41-B3AF-72D8F884D3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16360" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
   </bookViews>
@@ -390,47 +390,7 @@
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="59">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="42">
     <dxf>
       <font>
         <b/>
@@ -496,8 +456,17 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <border>
         <left style="hair">
           <color indexed="64"/>
@@ -517,10 +486,15 @@
       <font>
         <b/>
         <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <border>
         <left style="hair">
           <color indexed="64"/>
@@ -538,10 +512,220 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="16"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="31"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <left style="hair">
           <color indexed="64"/>
@@ -574,132 +758,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color theme="0" tint="-0.14996795556505021"/>
@@ -716,430 +774,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="16"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="31"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="16"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="31"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1628,32 +1262,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W15" totalsRowShown="0" headerRowDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W15" totalsRowShown="0" headerRowDxfId="41">
   <autoFilter ref="A3:W15" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}"/>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="49" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="48" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="47" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="46" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="45" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="44"/>
-    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="43"/>
-    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="42"/>
-    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="41"/>
-    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="40"/>
-    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="39"/>
-    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="38"/>
-    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="37"/>
-    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="36"/>
-    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="32" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="31" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="30" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="29" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="28" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="27"/>
+    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="26"/>
+    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="25"/>
+    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="24"/>
+    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="23"/>
+    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="22"/>
+    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="21"/>
+    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="20"/>
+    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="19"/>
+    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2840,90 +2474,57 @@
       <c r="W15" s="29"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="V5:V14">
-    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
-      <formula>"Cumplio Meta"</formula>
+  <conditionalFormatting sqref="A5:W14">
+    <cfRule type="expression" dxfId="17" priority="5">
+      <formula>$B5&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
-      <formula>"VM"</formula>
+    <cfRule type="expression" dxfId="16" priority="12">
+      <formula>$B5&lt;&gt;""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="22">
+      <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:R14 N5:N14">
-    <cfRule type="expression" dxfId="20" priority="23">
+    <cfRule type="expression" dxfId="14" priority="23">
       <formula>AND($B5&lt;&gt;"",$O5&lt;&gt;"2",,$O5&lt;&gt;"3")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="19" priority="19">
+    <cfRule type="expression" dxfId="13" priority="18">
+      <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="19">
       <formula>"y($B18&lt;&gt;"",r18&lt;36)"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="18" priority="18">
+  <conditionalFormatting sqref="Q5:Q14">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U9">
-    <cfRule type="expression" dxfId="17" priority="17">
-      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W14">
-    <cfRule type="expression" dxfId="16" priority="22">
-      <formula>$B5&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W14">
-    <cfRule type="expression" dxfId="15" priority="12">
-      <formula>$B5&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q14">
-    <cfRule type="expression" dxfId="14" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:R14">
-    <cfRule type="expression" dxfId="13" priority="15">
+    <cfRule type="expression" dxfId="9" priority="8">
+      <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="15">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5:U14">
-    <cfRule type="expression" dxfId="12" priority="16">
+    <cfRule type="expression" dxfId="7" priority="9">
+      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="16">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V14">
-    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
-      <formula>"Cumplio Meta"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
-      <formula>"VM"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W5:W14">
-    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="No cumple">
-      <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W14">
-    <cfRule type="expression" dxfId="8" priority="5">
-      <formula>$B5&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q14">
-    <cfRule type="expression" dxfId="7" priority="4">
-      <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R14">
-    <cfRule type="expression" dxfId="6" priority="8">
-      <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U14">
-    <cfRule type="expression" dxfId="5" priority="9">
-      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
+  <conditionalFormatting sqref="U10:U14">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>AND($B10&lt;&gt;"",U10&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:V14">
@@ -2933,23 +2534,20 @@
     <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="13" operator="equal">
+      <formula>"Cumplio Meta"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"VM"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:W14">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="No cumple">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="No cumple">
       <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q10:Q14">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND($B10&lt;&gt;"",Q10&lt;36)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U10:U14">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND($B10&lt;&gt;"",U10&lt;95000)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/graduacion/graduacion.xlsx
+++ b/graduacion/graduacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/graduacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89D1F8C-3D05-3E41-B3AF-72D8F884D3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22B5483-0FDD-C44D-9483-13BC7FBAF523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16360" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
+    <workbookView xWindow="0" yWindow="520" windowWidth="24460" windowHeight="16320" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
     <t>TOTAL2</t>
   </si>
   <si>
-    <t>Avance al 13 de marzo de 2026.</t>
+    <t>Avance al 18 de marzo de 2026.</t>
   </si>
 </sst>
 </file>
@@ -390,7 +390,492 @@
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="42">
+  <dxfs count="65">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="16"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="31"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1262,32 +1747,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W15" totalsRowShown="0" headerRowDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W15" totalsRowShown="0" headerRowDxfId="64">
   <autoFilter ref="A3:W15" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}"/>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="32" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="31" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="30" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="29" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="28" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="27"/>
-    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="26"/>
-    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="25"/>
-    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="24"/>
-    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="23"/>
-    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="22"/>
-    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="21"/>
-    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="20"/>
-    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="19"/>
-    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="57"/>
+    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="56"/>
+    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="55" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="54" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="53" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="52" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="51" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="50"/>
+    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="49"/>
+    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="48"/>
+    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="47"/>
+    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="46"/>
+    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="45"/>
+    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="44"/>
+    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="43"/>
+    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="42"/>
+    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2035,13 +2520,13 @@
         <v>0</v>
       </c>
       <c r="S8" s="37">
-        <v>70195.740000000005</v>
+        <v>70944.649999999994</v>
       </c>
       <c r="T8" s="37">
         <v>492.87</v>
       </c>
       <c r="U8" s="38">
-        <v>70688.61</v>
+        <v>71437.52</v>
       </c>
       <c r="V8" s="20"/>
       <c r="W8" s="39"/>
@@ -2236,13 +2721,13 @@
         <v>0</v>
       </c>
       <c r="S11" s="37">
-        <v>26906.37</v>
+        <v>28789.11</v>
       </c>
       <c r="T11" s="37">
         <v>7460.28</v>
       </c>
       <c r="U11" s="38">
-        <v>34366.65</v>
+        <v>36249.39</v>
       </c>
       <c r="V11" s="20"/>
       <c r="W11" s="39"/>
@@ -2306,10 +2791,10 @@
         <v>83519.55</v>
       </c>
       <c r="T12" s="37">
-        <v>8793.7800000000007</v>
+        <v>9499.81</v>
       </c>
       <c r="U12" s="38">
-        <v>92313.33</v>
+        <v>93019.36</v>
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="39"/>
@@ -2437,13 +2922,13 @@
         <v>0</v>
       </c>
       <c r="S14" s="37">
-        <v>36877</v>
+        <v>37485.300000000003</v>
       </c>
       <c r="T14" s="37">
         <v>3198.71</v>
       </c>
       <c r="U14" s="38">
-        <v>40075.71</v>
+        <v>40684.01</v>
       </c>
       <c r="V14" s="20"/>
       <c r="W14" s="39"/>
@@ -2474,57 +2959,90 @@
       <c r="W15" s="29"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:W14">
-    <cfRule type="expression" dxfId="17" priority="5">
-      <formula>$B5&lt;&gt;""</formula>
+  <conditionalFormatting sqref="V5:V14">
+    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
+      <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="12">
-      <formula>$B5&lt;&gt;""</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="22">
-      <formula>$B5&lt;&gt;""</formula>
+    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
+      <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:R14 N5:N14">
-    <cfRule type="expression" dxfId="14" priority="23">
+    <cfRule type="expression" dxfId="20" priority="23">
       <formula>AND($B5&lt;&gt;"",$O5&lt;&gt;"2",,$O5&lt;&gt;"3")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="13" priority="18">
-      <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="19">
+    <cfRule type="expression" dxfId="19" priority="19">
       <formula>"y($B18&lt;&gt;"",r18&lt;36)"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q14">
-    <cfRule type="expression" dxfId="11" priority="2">
+  <conditionalFormatting sqref="Q5:Q9">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="11">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U5:U9">
+    <cfRule type="expression" dxfId="17" priority="17">
+      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:W14">
+    <cfRule type="expression" dxfId="16" priority="22">
+      <formula>$B5&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:W14">
+    <cfRule type="expression" dxfId="15" priority="12">
+      <formula>$B5&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q5:Q14">
+    <cfRule type="expression" dxfId="14" priority="11">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:R14">
-    <cfRule type="expression" dxfId="9" priority="8">
-      <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="15">
+    <cfRule type="expression" dxfId="13" priority="15">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5:U14">
-    <cfRule type="expression" dxfId="7" priority="9">
-      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="16">
+    <cfRule type="expression" dxfId="12" priority="16">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U10:U14">
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>AND($B10&lt;&gt;"",U10&lt;95000)</formula>
+  <conditionalFormatting sqref="V5:V14">
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
+      <formula>"Cumplio Meta"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
+      <formula>"VM"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W5:W14">
+    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="No cumple">
+      <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:W14">
+    <cfRule type="expression" dxfId="8" priority="5">
+      <formula>$B5&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q5:Q14">
+    <cfRule type="expression" dxfId="7" priority="4">
+      <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:R14">
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U5:U14">
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:V14">
@@ -2534,16 +3052,20 @@
     <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="13" operator="equal">
-      <formula>"Cumplio Meta"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
-      <formula>"VM"</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W5:W14">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="No cumple">
+      <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W5:W14">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="No cumple">
-      <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
+  <conditionalFormatting sqref="Q10:Q14">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND($B10&lt;&gt;"",Q10&lt;36)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U10:U14">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND($B10&lt;&gt;"",U10&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/graduacion/graduacion.xlsx
+++ b/graduacion/graduacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/graduacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22B5483-0FDD-C44D-9483-13BC7FBAF523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77394F4-690A-6945-B8AD-6133FF991EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="520" windowWidth="24460" windowHeight="16320" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
     <t>TOTAL2</t>
   </si>
   <si>
-    <t>Avance al 18 de marzo de 2026.</t>
+    <t>Avance al 25 de marzo de 2026.</t>
   </si>
 </sst>
 </file>
@@ -2386,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="S6" s="37">
-        <v>45727.57</v>
+        <v>46326.04</v>
       </c>
       <c r="T6" s="37">
         <v>0</v>
       </c>
       <c r="U6" s="38">
-        <v>45727.57</v>
+        <v>46326.04</v>
       </c>
       <c r="V6" s="20"/>
       <c r="W6" s="39"/>
@@ -2520,13 +2520,13 @@
         <v>0</v>
       </c>
       <c r="S8" s="37">
-        <v>70944.649999999994</v>
+        <v>71990.28</v>
       </c>
       <c r="T8" s="37">
         <v>492.87</v>
       </c>
       <c r="U8" s="38">
-        <v>71437.52</v>
+        <v>72483.149999999994</v>
       </c>
       <c r="V8" s="20"/>
       <c r="W8" s="39"/>
@@ -2587,13 +2587,13 @@
         <v>0</v>
       </c>
       <c r="S9" s="37">
-        <v>77467.86</v>
+        <v>77980.33</v>
       </c>
       <c r="T9" s="37">
         <v>17462.349999999999</v>
       </c>
       <c r="U9" s="38">
-        <v>94930.21</v>
+        <v>95442.68</v>
       </c>
       <c r="V9" s="20"/>
       <c r="W9" s="39"/>
@@ -2645,22 +2645,22 @@
         <v>6.5</v>
       </c>
       <c r="P10" s="35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="36">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="R10" s="36">
         <v>0</v>
       </c>
       <c r="S10" s="37">
-        <v>23170.33</v>
+        <v>23743.95</v>
       </c>
       <c r="T10" s="37">
         <v>2343.7399999999998</v>
       </c>
       <c r="U10" s="38">
-        <v>25514.07</v>
+        <v>26087.69</v>
       </c>
       <c r="V10" s="20"/>
       <c r="W10" s="39"/>
@@ -2709,25 +2709,25 @@
         <v>30</v>
       </c>
       <c r="O11" s="34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P11" s="35">
         <v>1</v>
       </c>
       <c r="Q11" s="36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R11" s="36">
         <v>0</v>
       </c>
       <c r="S11" s="37">
-        <v>28789.11</v>
+        <v>29280.560000000001</v>
       </c>
       <c r="T11" s="37">
         <v>7460.28</v>
       </c>
       <c r="U11" s="38">
-        <v>36249.39</v>
+        <v>36740.839999999997</v>
       </c>
       <c r="V11" s="20"/>
       <c r="W11" s="39"/>
@@ -2776,25 +2776,25 @@
         <v>30</v>
       </c>
       <c r="O12" s="34">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="P12" s="35">
         <v>0</v>
       </c>
       <c r="Q12" s="36">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="R12" s="36">
         <v>0</v>
       </c>
       <c r="S12" s="37">
-        <v>83519.55</v>
+        <v>91675.03</v>
       </c>
       <c r="T12" s="37">
-        <v>9499.81</v>
+        <v>9781.07</v>
       </c>
       <c r="U12" s="38">
-        <v>93019.36</v>
+        <v>101456.1</v>
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="39"/>
@@ -2843,13 +2843,13 @@
         <v>30</v>
       </c>
       <c r="O13" s="34">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="P13" s="35">
         <v>0</v>
       </c>
       <c r="Q13" s="36">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="R13" s="36">
         <v>0</v>
@@ -2858,10 +2858,10 @@
         <v>51820.11</v>
       </c>
       <c r="T13" s="37">
-        <v>7384.25</v>
+        <v>10494.78</v>
       </c>
       <c r="U13" s="38">
-        <v>59204.36</v>
+        <v>62314.89</v>
       </c>
       <c r="V13" s="20"/>
       <c r="W13" s="39"/>

--- a/graduacion/graduacion.xlsx
+++ b/graduacion/graduacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/graduacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77394F4-690A-6945-B8AD-6133FF991EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130DA744-2335-274D-A0D3-10E5DB1BF520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="45">
   <si>
     <t>PÓLIZAS</t>
   </si>
@@ -164,7 +164,13 @@
     <t>TOTAL2</t>
   </si>
   <si>
-    <t>Avance al 25 de marzo de 2026.</t>
+    <t>PAULA ANGELICA LOMELI CAZARES</t>
+  </si>
+  <si>
+    <t>VM</t>
+  </si>
+  <si>
+    <t>Avance al 31 de marzo de 2026.</t>
   </si>
 </sst>
 </file>
@@ -2113,7 +2119,7 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2453,13 +2459,13 @@
         <v>0</v>
       </c>
       <c r="S7" s="37">
-        <v>63457.279999999999</v>
+        <v>64634.61</v>
       </c>
       <c r="T7" s="37">
         <v>35462.339999999997</v>
       </c>
       <c r="U7" s="38">
-        <v>98919.62</v>
+        <v>100096.95</v>
       </c>
       <c r="V7" s="20"/>
       <c r="W7" s="39"/>
@@ -2520,13 +2526,13 @@
         <v>0</v>
       </c>
       <c r="S8" s="37">
-        <v>71990.28</v>
+        <v>77872.639999999999</v>
       </c>
       <c r="T8" s="37">
         <v>492.87</v>
       </c>
       <c r="U8" s="38">
-        <v>72483.149999999994</v>
+        <v>78365.509999999995</v>
       </c>
       <c r="V8" s="20"/>
       <c r="W8" s="39"/>
@@ -2654,13 +2660,13 @@
         <v>0</v>
       </c>
       <c r="S10" s="37">
-        <v>23743.95</v>
+        <v>24339.67</v>
       </c>
       <c r="T10" s="37">
         <v>2343.7399999999998</v>
       </c>
       <c r="U10" s="38">
-        <v>26087.69</v>
+        <v>26683.41</v>
       </c>
       <c r="V10" s="20"/>
       <c r="W10" s="39"/>
@@ -2721,13 +2727,13 @@
         <v>0</v>
       </c>
       <c r="S11" s="37">
-        <v>29280.560000000001</v>
+        <v>30025.279999999999</v>
       </c>
       <c r="T11" s="37">
-        <v>7460.28</v>
+        <v>10725.48</v>
       </c>
       <c r="U11" s="38">
-        <v>36740.839999999997</v>
+        <v>40750.76</v>
       </c>
       <c r="V11" s="20"/>
       <c r="W11" s="39"/>
@@ -2788,13 +2794,13 @@
         <v>0</v>
       </c>
       <c r="S12" s="37">
-        <v>91675.03</v>
+        <v>93852.6</v>
       </c>
       <c r="T12" s="37">
         <v>9781.07</v>
       </c>
       <c r="U12" s="38">
-        <v>101456.1</v>
+        <v>103633.67</v>
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="39"/>
@@ -2855,13 +2861,13 @@
         <v>0</v>
       </c>
       <c r="S13" s="37">
-        <v>51820.11</v>
+        <v>62143.38</v>
       </c>
       <c r="T13" s="37">
-        <v>10494.78</v>
+        <v>11097.86</v>
       </c>
       <c r="U13" s="38">
-        <v>62314.89</v>
+        <v>73241.240000000005</v>
       </c>
       <c r="V13" s="20"/>
       <c r="W13" s="39"/>
@@ -2922,44 +2928,88 @@
         <v>0</v>
       </c>
       <c r="S14" s="37">
-        <v>37485.300000000003</v>
+        <v>38640.239999999998</v>
       </c>
       <c r="T14" s="37">
         <v>3198.71</v>
       </c>
       <c r="U14" s="38">
-        <v>40684.01</v>
+        <v>41838.949999999997</v>
       </c>
       <c r="V14" s="20"/>
       <c r="W14" s="39"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="27"/>
-      <c r="Q15" s="27"/>
-      <c r="R15" s="27"/>
-      <c r="S15" s="28"/>
-      <c r="T15" s="28"/>
-      <c r="U15" s="28"/>
-      <c r="V15" s="26"/>
-      <c r="W15" s="29"/>
+      <c r="A15" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="10">
+        <v>2043</v>
+      </c>
+      <c r="E15" s="10">
+        <v>2856</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="10">
+        <v>116876</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="31">
+        <v>1</v>
+      </c>
+      <c r="J15" s="32">
+        <v>46111</v>
+      </c>
+      <c r="K15" s="32">
+        <v>46111</v>
+      </c>
+      <c r="L15" s="6">
+        <v>46419</v>
+      </c>
+      <c r="M15" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" s="34">
+        <v>4.5</v>
+      </c>
+      <c r="P15" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="36">
+        <v>4.5</v>
+      </c>
+      <c r="R15" s="36">
+        <v>0</v>
+      </c>
+      <c r="S15" s="37">
+        <v>21055.42</v>
+      </c>
+      <c r="T15" s="37">
+        <v>188.11</v>
+      </c>
+      <c r="U15" s="38">
+        <v>21243.53</v>
+      </c>
+      <c r="V15" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W15" s="39"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="V5:V14">
+  <conditionalFormatting sqref="V5:V15">
     <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
@@ -2967,7 +3017,7 @@
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5:R14 N5:N14">
+  <conditionalFormatting sqref="P5:R15 N5:N15">
     <cfRule type="expression" dxfId="20" priority="23">
       <formula>AND($B5&lt;&gt;"",$O5&lt;&gt;"2",,$O5&lt;&gt;"3")</formula>
     </cfRule>
@@ -2987,32 +3037,32 @@
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W14">
+  <conditionalFormatting sqref="A5:W15">
     <cfRule type="expression" dxfId="16" priority="22">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W14">
+  <conditionalFormatting sqref="A5:W15">
     <cfRule type="expression" dxfId="15" priority="12">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q14">
+  <conditionalFormatting sqref="Q5:Q15">
     <cfRule type="expression" dxfId="14" priority="11">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R14">
+  <conditionalFormatting sqref="R5:R15">
     <cfRule type="expression" dxfId="13" priority="15">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U14">
+  <conditionalFormatting sqref="U5:U15">
     <cfRule type="expression" dxfId="12" priority="16">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V14">
+  <conditionalFormatting sqref="V5:V15">
     <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
@@ -3020,32 +3070,32 @@
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W5:W14">
+  <conditionalFormatting sqref="W5:W15">
     <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="No cumple">
       <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W14">
+  <conditionalFormatting sqref="A5:W15">
     <cfRule type="expression" dxfId="8" priority="5">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q14">
+  <conditionalFormatting sqref="Q5:Q15">
     <cfRule type="expression" dxfId="7" priority="4">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R14">
+  <conditionalFormatting sqref="R5:R15">
     <cfRule type="expression" dxfId="6" priority="8">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U14">
+  <conditionalFormatting sqref="U5:U15">
     <cfRule type="expression" dxfId="5" priority="9">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V14">
+  <conditionalFormatting sqref="V5:V15">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
@@ -3053,17 +3103,17 @@
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W5:W14">
+  <conditionalFormatting sqref="W5:W15">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="No cumple">
       <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q10:Q14">
+  <conditionalFormatting sqref="Q10:Q15">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>AND($B10&lt;&gt;"",Q10&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U10:U14">
+  <conditionalFormatting sqref="U10:U15">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND($B10&lt;&gt;"",U10&lt;95000)</formula>
     </cfRule>

--- a/graduacion/graduacion.xlsx
+++ b/graduacion/graduacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/graduacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130DA744-2335-274D-A0D3-10E5DB1BF520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12830784-7FAE-B64A-BE04-3904AD81DBDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
   </bookViews>
@@ -396,47 +396,7 @@
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="65">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="42">
     <dxf>
       <font>
         <b/>
@@ -502,6 +462,100 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFFF0000"/>
       </font>
       <border>
@@ -546,8 +600,138 @@
       <font>
         <b/>
         <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="16"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="31"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <left style="hair">
           <color indexed="64"/>
@@ -580,132 +764,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color theme="0" tint="-0.14996795556505021"/>
@@ -722,549 +780,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="16"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="31"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="16"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="31"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1753,32 +1268,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W15" totalsRowShown="0" headerRowDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W15" totalsRowShown="0" headerRowDxfId="41">
   <autoFilter ref="A3:W15" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}"/>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="57"/>
-    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="56"/>
-    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="55" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="54" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="53" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="52" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="51" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="50"/>
-    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="49"/>
-    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="48"/>
-    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="47"/>
-    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="46"/>
-    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="45"/>
-    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="44"/>
-    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="43"/>
-    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="42"/>
-    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="32" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="31" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="30" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="29" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="28" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="27"/>
+    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="26"/>
+    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="25"/>
+    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="24"/>
+    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="23"/>
+    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="22"/>
+    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="21"/>
+    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="20"/>
+    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="19"/>
+    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3009,90 +2524,57 @@
       <c r="W15" s="39"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="V5:V15">
-    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
-      <formula>"Cumplio Meta"</formula>
+  <conditionalFormatting sqref="A5:W15">
+    <cfRule type="expression" dxfId="17" priority="5">
+      <formula>$B5&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
-      <formula>"VM"</formula>
+    <cfRule type="expression" dxfId="16" priority="12">
+      <formula>$B5&lt;&gt;""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="22">
+      <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:R15 N5:N15">
-    <cfRule type="expression" dxfId="20" priority="23">
+    <cfRule type="expression" dxfId="14" priority="23">
       <formula>AND($B5&lt;&gt;"",$O5&lt;&gt;"2",,$O5&lt;&gt;"3")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="19" priority="19">
+    <cfRule type="expression" dxfId="13" priority="18">
+      <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="19">
       <formula>"y($B18&lt;&gt;"",r18&lt;36)"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="18" priority="18">
+  <conditionalFormatting sqref="Q5:Q15">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U9">
-    <cfRule type="expression" dxfId="17" priority="17">
-      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W15">
-    <cfRule type="expression" dxfId="16" priority="22">
-      <formula>$B5&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W15">
-    <cfRule type="expression" dxfId="15" priority="12">
-      <formula>$B5&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q15">
-    <cfRule type="expression" dxfId="14" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:R15">
-    <cfRule type="expression" dxfId="13" priority="15">
+    <cfRule type="expression" dxfId="9" priority="8">
+      <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="15">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5:U15">
-    <cfRule type="expression" dxfId="12" priority="16">
+    <cfRule type="expression" dxfId="7" priority="9">
+      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="16">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V15">
-    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
-      <formula>"Cumplio Meta"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
-      <formula>"VM"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W5:W15">
-    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="No cumple">
-      <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W15">
-    <cfRule type="expression" dxfId="8" priority="5">
-      <formula>$B5&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q15">
-    <cfRule type="expression" dxfId="7" priority="4">
-      <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R15">
-    <cfRule type="expression" dxfId="6" priority="8">
-      <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U15">
-    <cfRule type="expression" dxfId="5" priority="9">
-      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
+  <conditionalFormatting sqref="U10:U15">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>AND($B10&lt;&gt;"",U10&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:V15">
@@ -3102,20 +2584,16 @@
     <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="13" operator="equal">
+      <formula>"Cumplio Meta"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"VM"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:W15">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="No cumple">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="No cumple">
       <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q10:Q15">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND($B10&lt;&gt;"",Q10&lt;36)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U10:U15">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND($B10&lt;&gt;"",U10&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/graduacion/graduacion.xlsx
+++ b/graduacion/graduacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/graduacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12830784-7FAE-B64A-BE04-3904AD81DBDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDF9247-5EA7-704B-9383-C51E46CF306E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
+    <workbookView xWindow="3620" yWindow="4700" windowWidth="24460" windowHeight="16320" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -396,7 +396,492 @@
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="42">
+  <dxfs count="65">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="16"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="31"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1268,32 +1753,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W15" totalsRowShown="0" headerRowDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W15" totalsRowShown="0" headerRowDxfId="64">
   <autoFilter ref="A3:W15" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}"/>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="32" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="31" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="30" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="29" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="28" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="27"/>
-    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="26"/>
-    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="25"/>
-    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="24"/>
-    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="23"/>
-    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="22"/>
-    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="21"/>
-    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="20"/>
-    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="19"/>
-    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="57"/>
+    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="56"/>
+    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="55" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="54" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="53" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="52" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="51" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="50"/>
+    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="49"/>
+    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="48"/>
+    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="47"/>
+    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="46"/>
+    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="45"/>
+    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="44"/>
+    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="43"/>
+    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="42"/>
+    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2524,57 +3009,90 @@
       <c r="W15" s="39"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:W15">
-    <cfRule type="expression" dxfId="17" priority="5">
-      <formula>$B5&lt;&gt;""</formula>
+  <conditionalFormatting sqref="V5:V15">
+    <cfRule type="cellIs" dxfId="22" priority="22" operator="equal">
+      <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="12">
-      <formula>$B5&lt;&gt;""</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="22">
-      <formula>$B5&lt;&gt;""</formula>
+    <cfRule type="cellIs" dxfId="21" priority="22" operator="equal">
+      <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:R15 N5:N15">
-    <cfRule type="expression" dxfId="14" priority="23">
+    <cfRule type="expression" dxfId="20" priority="23">
       <formula>AND($B5&lt;&gt;"",$O5&lt;&gt;"2",,$O5&lt;&gt;"3")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="13" priority="18">
-      <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="19">
+    <cfRule type="expression" dxfId="19" priority="20">
       <formula>"y($B18&lt;&gt;"",r18&lt;36)"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q15">
-    <cfRule type="expression" dxfId="11" priority="2">
+  <conditionalFormatting sqref="Q5:Q9">
+    <cfRule type="expression" dxfId="18" priority="19">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="11">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U5:U9">
+    <cfRule type="expression" dxfId="17" priority="18">
+      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:W15">
+    <cfRule type="expression" dxfId="16" priority="22">
+      <formula>$B5&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:W15">
+    <cfRule type="expression" dxfId="15" priority="16">
+      <formula>$B5&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q5:Q15">
+    <cfRule type="expression" dxfId="14" priority="15">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:R15">
-    <cfRule type="expression" dxfId="9" priority="8">
-      <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="15">
+    <cfRule type="expression" dxfId="13" priority="15">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5:U15">
-    <cfRule type="expression" dxfId="7" priority="9">
-      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="16">
+    <cfRule type="expression" dxfId="12" priority="16">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U10:U15">
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>AND($B10&lt;&gt;"",U10&lt;95000)</formula>
+  <conditionalFormatting sqref="V5:V15">
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
+      <formula>"Cumplio Meta"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
+      <formula>"VM"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W5:W15">
+    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="No cumple">
+      <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:W15">
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>$B5&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q5:Q15">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:R15">
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U5:U15">
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:V15">
@@ -2584,16 +3102,20 @@
     <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="13" operator="equal">
-      <formula>"Cumplio Meta"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
-      <formula>"VM"</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W5:W15">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="No cumple">
+      <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W5:W15">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="No cumple">
-      <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
+  <conditionalFormatting sqref="Q10:Q15">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND($B10&lt;&gt;"",Q10&lt;36)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U10:U15">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND($B10&lt;&gt;"",U10&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/graduacion/graduacion.xlsx
+++ b/graduacion/graduacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/graduacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDF9247-5EA7-704B-9383-C51E46CF306E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3603B9B-65F7-5D49-AFF3-ED55352E5AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3620" yWindow="4700" windowWidth="24460" windowHeight="16320" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
+    <workbookView xWindow="2260" yWindow="1460" windowWidth="24460" windowHeight="16320" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="45">
   <si>
     <t>PÓLIZAS</t>
   </si>
@@ -167,10 +167,10 @@
     <t>PAULA ANGELICA LOMELI CAZARES</t>
   </si>
   <si>
-    <t>VM</t>
-  </si>
-  <si>
-    <t>Avance al 31 de marzo de 2026.</t>
+    <t>SOFIA CAMPILLO VASCONCELOS</t>
+  </si>
+  <si>
+    <t>Avance al 24 de abril de 2026.</t>
   </si>
 </sst>
 </file>
@@ -1003,68 +1003,82 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B0F0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+        <name val="Cambria"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
       </font>
       <border>
         <left style="hair">
@@ -1753,8 +1767,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W15" totalsRowShown="0" headerRowDxfId="64">
-  <autoFilter ref="A3:W15" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W16" totalsRowShown="0" headerRowDxfId="64">
+  <autoFilter ref="A3:W16" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="63"/>
     <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="62"/>
@@ -2101,7 +2115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52C454C9-C0D9-734E-BED4-594891A853F9}">
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
@@ -2295,7 +2309,7 @@
         <v>28</v>
       </c>
       <c r="I5" s="31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5" s="32">
         <v>45707</v>
@@ -2316,10 +2330,10 @@
         <v>11.5</v>
       </c>
       <c r="P5" s="35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q5" s="36">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="R5" s="36">
         <v>0</v>
@@ -2362,7 +2376,7 @@
         <v>31</v>
       </c>
       <c r="I6" s="31">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6" s="32">
         <v>45776</v>
@@ -2374,7 +2388,7 @@
         <v>46082</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N6" s="10" t="s">
         <v>30</v>
@@ -2429,7 +2443,7 @@
         <v>33</v>
       </c>
       <c r="I7" s="31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" s="32">
         <v>45806</v>
@@ -2459,13 +2473,13 @@
         <v>0</v>
       </c>
       <c r="S7" s="37">
-        <v>64634.61</v>
+        <v>66175.31</v>
       </c>
       <c r="T7" s="37">
         <v>35462.339999999997</v>
       </c>
       <c r="U7" s="38">
-        <v>100096.95</v>
+        <v>101637.65</v>
       </c>
       <c r="V7" s="20"/>
       <c r="W7" s="39"/>
@@ -2496,7 +2510,7 @@
         <v>34</v>
       </c>
       <c r="I8" s="31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8" s="32">
         <v>45863</v>
@@ -2526,13 +2540,13 @@
         <v>0</v>
       </c>
       <c r="S8" s="37">
-        <v>77872.639999999999</v>
+        <v>80016.08</v>
       </c>
       <c r="T8" s="37">
         <v>492.87</v>
       </c>
       <c r="U8" s="38">
-        <v>78365.509999999995</v>
+        <v>80508.95</v>
       </c>
       <c r="V8" s="20"/>
       <c r="W8" s="39"/>
@@ -2551,7 +2565,7 @@
         <v>2043</v>
       </c>
       <c r="E9" s="10">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="F9" s="30" t="s">
         <v>27</v>
@@ -2563,7 +2577,7 @@
         <v>35</v>
       </c>
       <c r="I9" s="31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9" s="32">
         <v>45852</v>
@@ -2593,13 +2607,13 @@
         <v>0</v>
       </c>
       <c r="S9" s="37">
-        <v>77980.33</v>
+        <v>80986.17</v>
       </c>
       <c r="T9" s="37">
         <v>17462.349999999999</v>
       </c>
       <c r="U9" s="38">
-        <v>95442.68</v>
+        <v>98448.52</v>
       </c>
       <c r="V9" s="20"/>
       <c r="W9" s="39"/>
@@ -2618,7 +2632,7 @@
         <v>2043</v>
       </c>
       <c r="E10" s="10">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="F10" s="30" t="s">
         <v>27</v>
@@ -2630,7 +2644,7 @@
         <v>36</v>
       </c>
       <c r="I10" s="31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J10" s="32">
         <v>45930</v>
@@ -2651,10 +2665,10 @@
         <v>6.5</v>
       </c>
       <c r="P10" s="35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="36">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="R10" s="36">
         <v>0</v>
@@ -2685,7 +2699,7 @@
         <v>2043</v>
       </c>
       <c r="E11" s="10">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="F11" s="30" t="s">
         <v>27</v>
@@ -2697,7 +2711,7 @@
         <v>37</v>
       </c>
       <c r="I11" s="31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" s="32">
         <v>45904</v>
@@ -2715,25 +2729,25 @@
         <v>30</v>
       </c>
       <c r="O11" s="34">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="P11" s="35">
         <v>1</v>
       </c>
       <c r="Q11" s="36">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="R11" s="36">
         <v>0</v>
       </c>
       <c r="S11" s="37">
-        <v>30025.279999999999</v>
+        <v>31114.74</v>
       </c>
       <c r="T11" s="37">
-        <v>10725.48</v>
+        <v>15687.95</v>
       </c>
       <c r="U11" s="38">
-        <v>40750.76</v>
+        <v>46802.69</v>
       </c>
       <c r="V11" s="20"/>
       <c r="W11" s="39"/>
@@ -2764,7 +2778,7 @@
         <v>38</v>
       </c>
       <c r="I12" s="31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12" s="32">
         <v>45944</v>
@@ -2794,13 +2808,13 @@
         <v>0</v>
       </c>
       <c r="S12" s="37">
-        <v>93852.6</v>
+        <v>95363.56</v>
       </c>
       <c r="T12" s="37">
-        <v>9781.07</v>
+        <v>10768.36</v>
       </c>
       <c r="U12" s="38">
-        <v>103633.67</v>
+        <v>106131.92</v>
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="39"/>
@@ -2831,7 +2845,7 @@
         <v>39</v>
       </c>
       <c r="I13" s="31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13" s="32">
         <v>45986</v>
@@ -2864,10 +2878,10 @@
         <v>62143.38</v>
       </c>
       <c r="T13" s="37">
-        <v>11097.86</v>
+        <v>13860.35</v>
       </c>
       <c r="U13" s="38">
-        <v>73241.240000000005</v>
+        <v>76003.73</v>
       </c>
       <c r="V13" s="20"/>
       <c r="W13" s="39"/>
@@ -2898,7 +2912,7 @@
         <v>40</v>
       </c>
       <c r="I14" s="31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="32">
         <v>46010</v>
@@ -2928,13 +2942,13 @@
         <v>0</v>
       </c>
       <c r="S14" s="37">
-        <v>38640.239999999998</v>
+        <v>41011.31</v>
       </c>
       <c r="T14" s="37">
         <v>3198.71</v>
       </c>
       <c r="U14" s="38">
-        <v>41838.949999999997</v>
+        <v>44210.02</v>
       </c>
       <c r="V14" s="20"/>
       <c r="W14" s="39"/>
@@ -2965,7 +2979,7 @@
         <v>42</v>
       </c>
       <c r="I15" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="32">
         <v>46111</v>
@@ -3003,66 +3017,131 @@
       <c r="U15" s="38">
         <v>21243.53</v>
       </c>
-      <c r="V15" s="20" t="s">
-        <v>43</v>
-      </c>
+      <c r="V15" s="20"/>
       <c r="W15" s="39"/>
     </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="10">
+        <v>2043</v>
+      </c>
+      <c r="E16" s="10">
+        <v>2856</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="10">
+        <v>116883</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="31">
+        <v>1</v>
+      </c>
+      <c r="J16" s="32">
+        <v>46126</v>
+      </c>
+      <c r="K16" s="32">
+        <v>46126</v>
+      </c>
+      <c r="L16" s="6">
+        <v>46447</v>
+      </c>
+      <c r="M16" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O16" s="34">
+        <v>5.5</v>
+      </c>
+      <c r="P16" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="36">
+        <v>5.5</v>
+      </c>
+      <c r="R16" s="36">
+        <v>0</v>
+      </c>
+      <c r="S16" s="37">
+        <v>5866.67</v>
+      </c>
+      <c r="T16" s="37">
+        <v>2190.37</v>
+      </c>
+      <c r="U16" s="38">
+        <v>8057.04</v>
+      </c>
+      <c r="V16" s="20"/>
+      <c r="W16" s="39"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="V5:V15">
-    <cfRule type="cellIs" dxfId="22" priority="22" operator="equal">
+  <conditionalFormatting sqref="V5:V16">
+    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5:R15 N5:N15">
+  <conditionalFormatting sqref="P5:R16 N5:N16">
     <cfRule type="expression" dxfId="20" priority="23">
       <formula>AND($B5&lt;&gt;"",$O5&lt;&gt;"2",,$O5&lt;&gt;"3")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="19" priority="20">
+    <cfRule type="expression" dxfId="19" priority="19">
       <formula>"y($B18&lt;&gt;"",r18&lt;36)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="18" priority="19">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5:U9">
-    <cfRule type="expression" dxfId="17" priority="18">
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W15">
+  <conditionalFormatting sqref="A5:W16">
     <cfRule type="expression" dxfId="16" priority="22">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W15">
-    <cfRule type="expression" dxfId="15" priority="16">
+  <conditionalFormatting sqref="A5:W16">
+    <cfRule type="expression" dxfId="15" priority="12">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q15">
-    <cfRule type="expression" dxfId="14" priority="15">
+  <conditionalFormatting sqref="Q5:Q16">
+    <cfRule type="expression" dxfId="14" priority="11">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R15">
+  <conditionalFormatting sqref="R5:R16">
     <cfRule type="expression" dxfId="13" priority="15">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U15">
+  <conditionalFormatting sqref="U5:U16">
     <cfRule type="expression" dxfId="12" priority="16">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V15">
+  <conditionalFormatting sqref="V5:V16">
     <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
@@ -3070,32 +3149,32 @@
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W5:W15">
+  <conditionalFormatting sqref="W5:W16">
     <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="No cumple">
       <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W15">
-    <cfRule type="expression" dxfId="8" priority="9">
+  <conditionalFormatting sqref="A5:W16">
+    <cfRule type="expression" dxfId="8" priority="5">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q15">
-    <cfRule type="expression" dxfId="7" priority="8">
+  <conditionalFormatting sqref="Q5:Q16">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R15">
+  <conditionalFormatting sqref="R5:R16">
     <cfRule type="expression" dxfId="6" priority="8">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U15">
+  <conditionalFormatting sqref="U5:U16">
     <cfRule type="expression" dxfId="5" priority="9">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V15">
+  <conditionalFormatting sqref="V5:V16">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
@@ -3103,17 +3182,17 @@
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W5:W15">
+  <conditionalFormatting sqref="W5:W16">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="No cumple">
       <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q10:Q15">
+  <conditionalFormatting sqref="Q10:Q16">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>AND($B10&lt;&gt;"",Q10&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U10:U15">
+  <conditionalFormatting sqref="U10:U16">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND($B10&lt;&gt;"",U10&lt;95000)</formula>
     </cfRule>

--- a/graduacion/graduacion.xlsx
+++ b/graduacion/graduacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/graduacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3603B9B-65F7-5D49-AFF3-ED55352E5AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944E226E-D165-F24B-8619-6D50E596A5D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2260" yWindow="1460" windowWidth="24460" windowHeight="16320" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
+    <workbookView xWindow="2520" yWindow="1680" windowWidth="24460" windowHeight="16320" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="46">
   <si>
     <t>PÓLIZAS</t>
   </si>
@@ -170,7 +170,10 @@
     <t>SOFIA CAMPILLO VASCONCELOS</t>
   </si>
   <si>
-    <t>Avance al 24 de abril de 2026.</t>
+    <t>VM</t>
+  </si>
+  <si>
+    <t>Avance al 30 de abril de 2026.</t>
   </si>
 </sst>
 </file>
@@ -396,7 +399,7 @@
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="65">
+  <dxfs count="63">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -436,13 +439,6 @@
           <color indexed="64"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -583,13 +579,6 @@
       <font>
         <b/>
         <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
         <color rgb="FF00B0F0"/>
         <name val="Cambria"/>
         <scheme val="none"/>
@@ -1003,82 +992,68 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <border>
+        <left style="hair">
+          <color indexed="64"/>
+        </left>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
+        </top>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
       </font>
       <border>
         <left style="hair">
@@ -1767,32 +1742,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W16" totalsRowShown="0" headerRowDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W16" totalsRowShown="0" headerRowDxfId="62">
   <autoFilter ref="A3:W16" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}"/>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="57"/>
-    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="56"/>
-    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="55" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="54" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="53" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="52" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="51" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="50"/>
-    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="49"/>
-    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="48"/>
-    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="47"/>
-    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="46"/>
-    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="45"/>
-    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="44"/>
-    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="43"/>
-    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="42"/>
-    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="53" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="52" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="51" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="50" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="49" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="48"/>
+    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="47"/>
+    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="46"/>
+    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="45"/>
+    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="44"/>
+    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="43"/>
+    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="42"/>
+    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="41"/>
+    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="40"/>
+    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2133,7 +2108,7 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2473,13 +2448,13 @@
         <v>0</v>
       </c>
       <c r="S7" s="37">
-        <v>66175.31</v>
+        <v>67720.23</v>
       </c>
       <c r="T7" s="37">
         <v>35462.339999999997</v>
       </c>
       <c r="U7" s="38">
-        <v>101637.65</v>
+        <v>103182.57</v>
       </c>
       <c r="V7" s="20"/>
       <c r="W7" s="39"/>
@@ -2528,25 +2503,25 @@
         <v>30</v>
       </c>
       <c r="O8" s="34">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="P8" s="35">
         <v>1</v>
       </c>
       <c r="Q8" s="36">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="R8" s="36">
         <v>0</v>
       </c>
       <c r="S8" s="37">
-        <v>80016.08</v>
+        <v>90006.9</v>
       </c>
       <c r="T8" s="37">
         <v>492.87</v>
       </c>
       <c r="U8" s="38">
-        <v>80508.95</v>
+        <v>90499.77</v>
       </c>
       <c r="V8" s="20"/>
       <c r="W8" s="39"/>
@@ -2674,13 +2649,13 @@
         <v>0</v>
       </c>
       <c r="S10" s="37">
-        <v>24339.67</v>
+        <v>24918.63</v>
       </c>
       <c r="T10" s="37">
         <v>2343.7399999999998</v>
       </c>
       <c r="U10" s="38">
-        <v>26683.41</v>
+        <v>27262.37</v>
       </c>
       <c r="V10" s="20"/>
       <c r="W10" s="39"/>
@@ -2808,13 +2783,13 @@
         <v>0</v>
       </c>
       <c r="S12" s="37">
-        <v>95363.56</v>
+        <v>97554</v>
       </c>
       <c r="T12" s="37">
         <v>10768.36</v>
       </c>
       <c r="U12" s="38">
-        <v>106131.92</v>
+        <v>108322.36</v>
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="39"/>
@@ -2875,13 +2850,13 @@
         <v>0</v>
       </c>
       <c r="S13" s="37">
-        <v>62143.38</v>
+        <v>62946.02</v>
       </c>
       <c r="T13" s="37">
-        <v>13860.35</v>
+        <v>14463.43</v>
       </c>
       <c r="U13" s="38">
-        <v>76003.73</v>
+        <v>77409.45</v>
       </c>
       <c r="V13" s="20"/>
       <c r="W13" s="39"/>
@@ -2942,13 +2917,13 @@
         <v>0</v>
       </c>
       <c r="S14" s="37">
-        <v>41011.31</v>
+        <v>46665.87</v>
       </c>
       <c r="T14" s="37">
         <v>3198.71</v>
       </c>
       <c r="U14" s="38">
-        <v>44210.02</v>
+        <v>49864.58</v>
       </c>
       <c r="V14" s="20"/>
       <c r="W14" s="39"/>
@@ -3009,13 +2984,13 @@
         <v>0</v>
       </c>
       <c r="S15" s="37">
-        <v>21055.42</v>
+        <v>21667.65</v>
       </c>
       <c r="T15" s="37">
-        <v>188.11</v>
+        <v>376.22</v>
       </c>
       <c r="U15" s="38">
-        <v>21243.53</v>
+        <v>22043.87</v>
       </c>
       <c r="V15" s="20"/>
       <c r="W15" s="39"/>
@@ -3064,127 +3039,135 @@
         <v>30</v>
       </c>
       <c r="O16" s="34">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="P16" s="35">
         <v>0</v>
       </c>
       <c r="Q16" s="36">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="R16" s="36">
         <v>0</v>
       </c>
       <c r="S16" s="37">
-        <v>5866.67</v>
+        <v>17412.400000000001</v>
       </c>
       <c r="T16" s="37">
-        <v>2190.37</v>
+        <v>6085.44</v>
       </c>
       <c r="U16" s="38">
-        <v>8057.04</v>
-      </c>
-      <c r="V16" s="20"/>
+        <v>23497.84</v>
+      </c>
+      <c r="V16" s="20" t="s">
+        <v>44</v>
+      </c>
       <c r="W16" s="39"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="W5:W16">
+    <cfRule type="expression" dxfId="38" priority="26">
+      <formula>$B5&lt;&gt;""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="33">
+      <formula>$B5&lt;&gt;""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="43">
+      <formula>$B5&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W5:W16">
+    <cfRule type="containsText" dxfId="21" priority="24" operator="containsText" text="No cumple">
+      <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="V5:V16">
-    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="18" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="19" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:R16 N5:N16">
-    <cfRule type="expression" dxfId="20" priority="23">
+    <cfRule type="expression" dxfId="18" priority="21">
       <formula>AND($B5&lt;&gt;"",$O5&lt;&gt;"2",,$O5&lt;&gt;"3")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="19" priority="19">
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>"y($B18&lt;&gt;"",r18&lt;36)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="18" priority="18">
+    <cfRule type="expression" dxfId="16" priority="16">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5:U9">
-    <cfRule type="expression" dxfId="17" priority="17">
+    <cfRule type="expression" dxfId="15" priority="15">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W16">
-    <cfRule type="expression" dxfId="16" priority="22">
+  <conditionalFormatting sqref="A5:V16">
+    <cfRule type="expression" dxfId="14" priority="20">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W16">
-    <cfRule type="expression" dxfId="15" priority="12">
+  <conditionalFormatting sqref="A5:V16">
+    <cfRule type="expression" dxfId="13" priority="10">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q16">
-    <cfRule type="expression" dxfId="14" priority="11">
+    <cfRule type="expression" dxfId="12" priority="9">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:R16">
-    <cfRule type="expression" dxfId="13" priority="15">
+    <cfRule type="expression" dxfId="11" priority="13">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5:U16">
-    <cfRule type="expression" dxfId="12" priority="16">
+    <cfRule type="expression" dxfId="10" priority="14">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:V16">
-    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W5:W16">
-    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="No cumple">
-      <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:W16">
-    <cfRule type="expression" dxfId="8" priority="5">
+  <conditionalFormatting sqref="A5:V16">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q16">
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:R16">
-    <cfRule type="expression" dxfId="6" priority="8">
+    <cfRule type="expression" dxfId="5" priority="7">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5:U16">
-    <cfRule type="expression" dxfId="5" priority="9">
+    <cfRule type="expression" dxfId="4" priority="8">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:V16">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"VM"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W5:W16">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="No cumple">
-      <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q10:Q16">

--- a/graduacion/graduacion.xlsx
+++ b/graduacion/graduacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/graduacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944E226E-D165-F24B-8619-6D50E596A5D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5016FF17-750B-664F-8E2D-74B10189D4A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="1680" windowWidth="24460" windowHeight="16320" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
+    <workbookView xWindow="2400" yWindow="1440" windowWidth="24460" windowHeight="16320" xr2:uid="{C790F585-E5F8-714F-8D00-C112DB38F0A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="44">
   <si>
     <t>PÓLIZAS</t>
   </si>
@@ -122,9 +122,6 @@
     <t>ALEJANDRA GABRIELA AMBRIZ GOMEZ</t>
   </si>
   <si>
-    <t>CLAUDIA VALERIA HERNANDEZ MACIAS</t>
-  </si>
-  <si>
     <t>PROFESIONAL</t>
   </si>
   <si>
@@ -137,18 +134,12 @@
     <t>TRAINING ALLOWANCE</t>
   </si>
   <si>
-    <t>BRUNO BRAULIO MACIAS ALVAREZ</t>
-  </si>
-  <si>
     <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
   </si>
   <si>
     <t>ANA LAURA CONTRERAS IÐIGUEZ</t>
   </si>
   <si>
-    <t>MARIA JOSE GUZMAN ZAMORA</t>
-  </si>
-  <si>
     <t>HANA SOFIA LOPEZ QUIÐONEZ</t>
   </si>
   <si>
@@ -173,7 +164,10 @@
     <t>VM</t>
   </si>
   <si>
-    <t>Avance al 30 de abril de 2026.</t>
+    <t>MONSERRAT VELASCO SANTOS</t>
+  </si>
+  <si>
+    <t>Avance al 20 de MAYO de 2026.</t>
   </si>
 </sst>
 </file>
@@ -399,7 +393,7 @@
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="48">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -872,340 +866,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B0F0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF0070C0"/>
-        <name val="Cambria"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="16"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="31"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color indexed="64"/>
-        </left>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
-        </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border>
         <left style="hair">
           <color indexed="64"/>
@@ -1238,20 +898,11 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1742,32 +1393,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W16" totalsRowShown="0" headerRowDxfId="62">
-  <autoFilter ref="A3:W16" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}" name="Tabla1" displayName="Tabla1" ref="A3:W14" totalsRowShown="0" headerRowDxfId="47">
+  <autoFilter ref="A3:W14" xr:uid="{C8C84689-1448-8442-B1F2-C8CC1CDB3E89}"/>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="56"/>
-    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="55"/>
-    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="54"/>
-    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="53" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="52" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="51" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="50" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="49" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="48"/>
-    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="47"/>
-    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="46"/>
-    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="45"/>
-    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="44"/>
-    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="43"/>
-    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="42"/>
-    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="41"/>
-    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="40"/>
-    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{3B622300-6924-DB4F-A62F-2EEC39FAB0A2}" name="DIR / ZONA" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{56109AD6-9361-EA49-82CB-5F16E0E8FEF7}" name="OFICINA" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{AB1E1DBC-B048-A740-9A78-5965EB9EC44F}" name="GERENCIA / SP" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{61CAAE43-B726-6C46-97AC-90058F4DA6D1}" name="MAT" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{E8AA5DF5-9B6D-2543-9325-7C035D241238}" name="SUC" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{295631B1-0185-9B4D-8500-6B9AA08F63F2}" name="PROMOTOR / PARTNER" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{4B47B735-008D-2449-B456-D2DD3B472696}" name="ASESOR" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{975EC707-F2EE-5144-BEFE-BA96A47202F3}" name="NOMBRE" dataDxfId="39"/>
+    <tableColumn id="9" xr3:uid="{027BA34A-24D8-E94B-83B2-B0C1B6025207}" name="MES" dataDxfId="38" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{646ECA88-7396-D040-B5DF-0AAEB243F28F}" name="F. CONEXIÓN" dataDxfId="37" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{26CD5808-6FE4-1F4D-BE8F-7814A14EB008}" name="F. CONCURSO" dataDxfId="36" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{4B28D83F-5D6D-624E-BB91-9704EE1A3E14}" name="LÍMITE P/  LOGRO DE META" dataDxfId="35" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{E489BE13-FD5F-904D-8881-224954582674}" name="CUADERNO DE CONCURSO" dataDxfId="34" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{26915D16-D4BC-B145-BE2F-527AE56B2BAB}" name="GRUPO" dataDxfId="33"/>
+    <tableColumn id="15" xr3:uid="{A89792EE-9143-B14C-9C0C-81844C60721D}" name="TOTAL" dataDxfId="32"/>
+    <tableColumn id="16" xr3:uid="{14F06EE7-B141-B346-AB39-618B1114E96F}" name="CANCEL." dataDxfId="31"/>
+    <tableColumn id="17" xr3:uid="{9B9D77BF-8869-CA44-BCEA-33C8D4FA1307}" name="EN VIGOR" dataDxfId="30"/>
+    <tableColumn id="18" xr3:uid="{2060FD50-AB1E-C245-B146-DB9618552765}" name="PROMEDIO" dataDxfId="29"/>
+    <tableColumn id="19" xr3:uid="{F956BCDA-7715-ED46-9C68-AA2CA74FB455}" name="VIDA" dataDxfId="28"/>
+    <tableColumn id="20" xr3:uid="{F8F35AF9-120D-5944-B380-9F31E59F8709}" name="GMM" dataDxfId="27"/>
+    <tableColumn id="21" xr3:uid="{E6C3EA59-5FA1-3446-9DEF-1B9EE5CF332D}" name="TOTAL2" dataDxfId="26"/>
+    <tableColumn id="22" xr3:uid="{75E46555-9E6E-E349-A48E-06957BB9C039}" name="ESTATUS" dataDxfId="25"/>
+    <tableColumn id="23" xr3:uid="{24832D48-18B2-2F4B-A6BA-E52011154826}" name="OBSERVACIÓN" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2090,7 +1741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52C454C9-C0D9-734E-BED4-594891A853F9}">
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
@@ -2108,7 +1759,7 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2224,7 +1875,7 @@
         <v>21</v>
       </c>
       <c r="U3" s="13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="V3" s="19" t="s">
         <v>22</v>
@@ -2278,49 +1929,49 @@
         <v>27</v>
       </c>
       <c r="G5" s="10">
-        <v>111960</v>
+        <v>112522</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="31">
+        <v>14</v>
+      </c>
+      <c r="J5" s="32">
+        <v>45776</v>
+      </c>
+      <c r="K5" s="32">
+        <v>45776</v>
+      </c>
+      <c r="L5" s="6">
+        <v>46082</v>
+      </c>
+      <c r="M5" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="31">
-        <v>15</v>
-      </c>
-      <c r="J5" s="32">
-        <v>45707</v>
-      </c>
-      <c r="K5" s="32">
-        <v>45707</v>
-      </c>
-      <c r="L5" s="6">
-        <v>46023</v>
-      </c>
-      <c r="M5" s="33" t="s">
+      <c r="N5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="N5" s="10" t="s">
-        <v>30</v>
-      </c>
       <c r="O5" s="34">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="P5" s="35">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="36">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="R5" s="36">
         <v>0</v>
       </c>
       <c r="S5" s="37">
-        <v>98140.03</v>
+        <v>46326.04</v>
       </c>
       <c r="T5" s="37">
-        <v>934.52</v>
+        <v>0</v>
       </c>
       <c r="U5" s="38">
-        <v>99074.55</v>
+        <v>46326.04</v>
       </c>
       <c r="V5" s="20"/>
       <c r="W5" s="39"/>
@@ -2345,49 +1996,49 @@
         <v>27</v>
       </c>
       <c r="G6" s="10">
-        <v>112522</v>
+        <v>114100</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="31">
+        <v>11</v>
+      </c>
+      <c r="J6" s="32">
+        <v>45863</v>
+      </c>
+      <c r="K6" s="32">
+        <v>45863</v>
+      </c>
+      <c r="L6" s="6">
+        <v>46174</v>
+      </c>
+      <c r="M6" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="31">
-        <v>13</v>
-      </c>
-      <c r="J6" s="32">
-        <v>45776</v>
-      </c>
-      <c r="K6" s="32">
-        <v>45776</v>
-      </c>
-      <c r="L6" s="6">
-        <v>46082</v>
-      </c>
-      <c r="M6" s="33" t="s">
+      <c r="N6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="10" t="s">
-        <v>30</v>
-      </c>
       <c r="O6" s="34">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="P6" s="35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="36">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="R6" s="36">
         <v>0</v>
       </c>
       <c r="S6" s="37">
-        <v>46326.04</v>
+        <v>92155.07</v>
       </c>
       <c r="T6" s="37">
-        <v>0</v>
+        <v>492.87</v>
       </c>
       <c r="U6" s="38">
-        <v>46326.04</v>
+        <v>92647.94</v>
       </c>
       <c r="V6" s="20"/>
       <c r="W6" s="39"/>
@@ -2412,34 +2063,34 @@
         <v>27</v>
       </c>
       <c r="G7" s="10">
-        <v>113076</v>
+        <v>113450</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="I7" s="31">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J7" s="32">
-        <v>45806</v>
+        <v>45852</v>
       </c>
       <c r="K7" s="32">
-        <v>45806</v>
+        <v>45852</v>
       </c>
       <c r="L7" s="6">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="M7" s="33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O7" s="34">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="P7" s="35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="36">
         <v>10.5</v>
@@ -2448,13 +2099,13 @@
         <v>0</v>
       </c>
       <c r="S7" s="37">
-        <v>67720.23</v>
+        <v>80986.17</v>
       </c>
       <c r="T7" s="37">
-        <v>35462.339999999997</v>
+        <v>17462.349999999999</v>
       </c>
       <c r="U7" s="38">
-        <v>103182.57</v>
+        <v>98448.52</v>
       </c>
       <c r="V7" s="20"/>
       <c r="W7" s="39"/>
@@ -2473,55 +2124,55 @@
         <v>2043</v>
       </c>
       <c r="E8" s="10">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="F8" s="30" t="s">
         <v>27</v>
       </c>
       <c r="G8" s="10">
-        <v>114100</v>
+        <v>114157</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>34</v>
       </c>
       <c r="I8" s="31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" s="32">
-        <v>45863</v>
+        <v>45904</v>
       </c>
       <c r="K8" s="32">
-        <v>45863</v>
+        <v>45904</v>
       </c>
       <c r="L8" s="6">
-        <v>46174</v>
+        <v>46235</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O8" s="34">
-        <v>14.5</v>
+        <v>9.5</v>
       </c>
       <c r="P8" s="35">
         <v>1</v>
       </c>
       <c r="Q8" s="36">
-        <v>13.5</v>
+        <v>8.5</v>
       </c>
       <c r="R8" s="36">
         <v>0</v>
       </c>
       <c r="S8" s="37">
-        <v>90006.9</v>
+        <v>32957.629999999997</v>
       </c>
       <c r="T8" s="37">
-        <v>492.87</v>
+        <v>15687.95</v>
       </c>
       <c r="U8" s="38">
-        <v>90499.77</v>
+        <v>48645.58</v>
       </c>
       <c r="V8" s="20"/>
       <c r="W8" s="39"/>
@@ -2540,55 +2191,55 @@
         <v>2043</v>
       </c>
       <c r="E9" s="10">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="F9" s="30" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="10">
-        <v>113450</v>
+        <v>115047</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I9" s="31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J9" s="32">
-        <v>45852</v>
+        <v>45944</v>
       </c>
       <c r="K9" s="32">
-        <v>45852</v>
+        <v>45944</v>
       </c>
       <c r="L9" s="6">
-        <v>46174</v>
+        <v>46266</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O9" s="34">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="P9" s="35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="36">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="R9" s="36">
         <v>0</v>
       </c>
       <c r="S9" s="37">
-        <v>80986.17</v>
+        <v>101426.14</v>
       </c>
       <c r="T9" s="37">
-        <v>17462.349999999999</v>
+        <v>11474.39</v>
       </c>
       <c r="U9" s="38">
-        <v>98448.52</v>
+        <v>112900.53</v>
       </c>
       <c r="V9" s="20"/>
       <c r="W9" s="39"/>
@@ -2613,49 +2264,49 @@
         <v>27</v>
       </c>
       <c r="G10" s="10">
-        <v>114431</v>
+        <v>115404</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>36</v>
       </c>
       <c r="I10" s="31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J10" s="32">
-        <v>45930</v>
+        <v>45986</v>
       </c>
       <c r="K10" s="32">
-        <v>45930</v>
+        <v>45986</v>
       </c>
       <c r="L10" s="6">
-        <v>46235</v>
+        <v>46296</v>
       </c>
       <c r="M10" s="33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O10" s="34">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="P10" s="35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="36">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="R10" s="36">
         <v>0</v>
       </c>
       <c r="S10" s="37">
-        <v>24918.63</v>
+        <v>62946.02</v>
       </c>
       <c r="T10" s="37">
-        <v>2343.7399999999998</v>
+        <v>14463.43</v>
       </c>
       <c r="U10" s="38">
-        <v>27262.37</v>
+        <v>77409.45</v>
       </c>
       <c r="V10" s="20"/>
       <c r="W10" s="39"/>
@@ -2674,40 +2325,40 @@
         <v>2043</v>
       </c>
       <c r="E11" s="10">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="F11" s="30" t="s">
         <v>27</v>
       </c>
       <c r="G11" s="10">
-        <v>114157</v>
+        <v>116060</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I11" s="31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J11" s="32">
-        <v>45904</v>
+        <v>46010</v>
       </c>
       <c r="K11" s="32">
-        <v>45904</v>
+        <v>46010</v>
       </c>
       <c r="L11" s="6">
-        <v>46235</v>
+        <v>46327</v>
       </c>
       <c r="M11" s="33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O11" s="34">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="P11" s="35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="36">
         <v>8.5</v>
@@ -2716,13 +2367,13 @@
         <v>0</v>
       </c>
       <c r="S11" s="37">
-        <v>31114.74</v>
+        <v>48403.94</v>
       </c>
       <c r="T11" s="37">
-        <v>15687.95</v>
+        <v>3198.71</v>
       </c>
       <c r="U11" s="38">
-        <v>46802.69</v>
+        <v>51602.65</v>
       </c>
       <c r="V11" s="20"/>
       <c r="W11" s="39"/>
@@ -2747,49 +2398,49 @@
         <v>27</v>
       </c>
       <c r="G12" s="10">
-        <v>115047</v>
+        <v>116876</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I12" s="31">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J12" s="32">
-        <v>45944</v>
+        <v>46111</v>
       </c>
       <c r="K12" s="32">
-        <v>45944</v>
+        <v>46111</v>
       </c>
       <c r="L12" s="6">
-        <v>46266</v>
+        <v>46419</v>
       </c>
       <c r="M12" s="33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O12" s="34">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="P12" s="35">
         <v>0</v>
       </c>
       <c r="Q12" s="36">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="R12" s="36">
         <v>0</v>
       </c>
       <c r="S12" s="37">
-        <v>97554</v>
+        <v>21667.65</v>
       </c>
       <c r="T12" s="37">
-        <v>10768.36</v>
+        <v>376.22</v>
       </c>
       <c r="U12" s="38">
-        <v>108322.36</v>
+        <v>22043.87</v>
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="39"/>
@@ -2808,57 +2459,59 @@
         <v>2043</v>
       </c>
       <c r="E13" s="10">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>27</v>
       </c>
       <c r="G13" s="10">
-        <v>115404</v>
+        <v>116883</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I13" s="31">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J13" s="32">
-        <v>45986</v>
+        <v>46126</v>
       </c>
       <c r="K13" s="32">
-        <v>45986</v>
+        <v>46126</v>
       </c>
       <c r="L13" s="6">
-        <v>46296</v>
+        <v>46447</v>
       </c>
       <c r="M13" s="33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O13" s="34">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P13" s="35">
         <v>0</v>
       </c>
       <c r="Q13" s="36">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R13" s="36">
         <v>0</v>
       </c>
       <c r="S13" s="37">
-        <v>62946.02</v>
+        <v>17958.09</v>
       </c>
       <c r="T13" s="37">
-        <v>14463.43</v>
+        <v>6085.44</v>
       </c>
       <c r="U13" s="38">
-        <v>77409.45</v>
-      </c>
-      <c r="V13" s="20"/>
+        <v>24043.53</v>
+      </c>
+      <c r="V13" s="20" t="s">
+        <v>41</v>
+      </c>
       <c r="W13" s="39"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
@@ -2875,213 +2528,74 @@
         <v>2043</v>
       </c>
       <c r="E14" s="10">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="F14" s="30" t="s">
         <v>27</v>
       </c>
       <c r="G14" s="10">
-        <v>116060</v>
+        <v>117440</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I14" s="31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J14" s="32">
-        <v>46010</v>
+        <v>46149</v>
       </c>
       <c r="K14" s="32">
-        <v>46010</v>
+        <v>46149</v>
       </c>
       <c r="L14" s="6">
-        <v>46327</v>
+        <v>46478</v>
       </c>
       <c r="M14" s="33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O14" s="34">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="P14" s="35">
         <v>0</v>
       </c>
       <c r="Q14" s="36">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="R14" s="36">
         <v>0</v>
       </c>
       <c r="S14" s="37">
-        <v>46665.87</v>
+        <v>13539.81</v>
       </c>
       <c r="T14" s="37">
-        <v>3198.71</v>
+        <v>0</v>
       </c>
       <c r="U14" s="38">
-        <v>49864.58</v>
-      </c>
-      <c r="V14" s="20"/>
+        <v>13539.81</v>
+      </c>
+      <c r="V14" s="20" t="s">
+        <v>41</v>
+      </c>
       <c r="W14" s="39"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="10">
-        <v>2043</v>
-      </c>
-      <c r="E15" s="10">
-        <v>2856</v>
-      </c>
-      <c r="F15" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="10">
-        <v>116876</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" s="31">
-        <v>2</v>
-      </c>
-      <c r="J15" s="32">
-        <v>46111</v>
-      </c>
-      <c r="K15" s="32">
-        <v>46111</v>
-      </c>
-      <c r="L15" s="6">
-        <v>46419</v>
-      </c>
-      <c r="M15" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O15" s="34">
-        <v>4.5</v>
-      </c>
-      <c r="P15" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="36">
-        <v>4.5</v>
-      </c>
-      <c r="R15" s="36">
-        <v>0</v>
-      </c>
-      <c r="S15" s="37">
-        <v>21667.65</v>
-      </c>
-      <c r="T15" s="37">
-        <v>376.22</v>
-      </c>
-      <c r="U15" s="38">
-        <v>22043.87</v>
-      </c>
-      <c r="V15" s="20"/>
-      <c r="W15" s="39"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="10">
-        <v>2043</v>
-      </c>
-      <c r="E16" s="10">
-        <v>2856</v>
-      </c>
-      <c r="F16" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="10">
-        <v>116883</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="31">
-        <v>1</v>
-      </c>
-      <c r="J16" s="32">
-        <v>46126</v>
-      </c>
-      <c r="K16" s="32">
-        <v>46126</v>
-      </c>
-      <c r="L16" s="6">
-        <v>46447</v>
-      </c>
-      <c r="M16" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="N16" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O16" s="34">
-        <v>8</v>
-      </c>
-      <c r="P16" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <v>8</v>
-      </c>
-      <c r="R16" s="36">
-        <v>0</v>
-      </c>
-      <c r="S16" s="37">
-        <v>17412.400000000001</v>
-      </c>
-      <c r="T16" s="37">
-        <v>6085.44</v>
-      </c>
-      <c r="U16" s="38">
-        <v>23497.84</v>
-      </c>
-      <c r="V16" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="W16" s="39"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="W5:W16">
-    <cfRule type="expression" dxfId="38" priority="26">
+  <conditionalFormatting sqref="W5:W14">
+    <cfRule type="containsText" dxfId="23" priority="45" operator="containsText" text="No cumple">
+      <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="47">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="33">
-      <formula>$B5&lt;&gt;""</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="43">
+    <cfRule type="expression" dxfId="21" priority="64">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W5:W16">
-    <cfRule type="containsText" dxfId="21" priority="24" operator="containsText" text="No cumple">
-      <formula>NOT(ISERROR(SEARCH("No cumple",W5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V16">
+  <conditionalFormatting sqref="V5:V14">
     <cfRule type="cellIs" dxfId="20" priority="18" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
@@ -3089,52 +2603,52 @@
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5:R16 N5:N16">
+  <conditionalFormatting sqref="P5:R14 N5:N14">
     <cfRule type="expression" dxfId="18" priority="21">
       <formula>AND($B5&lt;&gt;"",$O5&lt;&gt;"2",,$O5&lt;&gt;"3")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q9">
+  <conditionalFormatting sqref="Q5:Q7">
     <cfRule type="expression" dxfId="17" priority="17">
       <formula>"y($B18&lt;&gt;"",r18&lt;36)"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q9">
+  <conditionalFormatting sqref="Q5:Q7">
     <cfRule type="expression" dxfId="16" priority="16">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U9">
+  <conditionalFormatting sqref="U5:U7">
     <cfRule type="expression" dxfId="15" priority="15">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:V16">
+  <conditionalFormatting sqref="A5:V14">
     <cfRule type="expression" dxfId="14" priority="20">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:V16">
+  <conditionalFormatting sqref="A5:V14">
     <cfRule type="expression" dxfId="13" priority="10">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q16">
+  <conditionalFormatting sqref="Q5:Q14">
     <cfRule type="expression" dxfId="12" priority="9">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R16">
+  <conditionalFormatting sqref="R5:R14">
     <cfRule type="expression" dxfId="11" priority="13">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U16">
+  <conditionalFormatting sqref="U5:U14">
     <cfRule type="expression" dxfId="10" priority="14">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V16">
+  <conditionalFormatting sqref="V5:V14">
     <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
@@ -3142,27 +2656,27 @@
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:V16">
+  <conditionalFormatting sqref="A5:V14">
     <cfRule type="expression" dxfId="7" priority="4">
       <formula>$B5&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:Q16">
+  <conditionalFormatting sqref="Q5:Q14">
     <cfRule type="expression" dxfId="6" priority="3">
       <formula>AND($B5&lt;&gt;"",Q5&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R16">
+  <conditionalFormatting sqref="R5:R14">
     <cfRule type="expression" dxfId="5" priority="7">
       <formula>AND($J5&gt;=13,$S5&lt;1,$B5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U16">
+  <conditionalFormatting sqref="U5:U14">
     <cfRule type="expression" dxfId="4" priority="8">
       <formula>AND($B5&lt;&gt;"",U5&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V16">
+  <conditionalFormatting sqref="V5:V14">
     <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"Cumplio Meta"</formula>
     </cfRule>
@@ -3170,14 +2684,14 @@
       <formula>"VM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q10:Q16">
+  <conditionalFormatting sqref="Q8:Q14">
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND($B10&lt;&gt;"",Q10&lt;36)</formula>
+      <formula>AND($B8&lt;&gt;"",Q8&lt;36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U10:U16">
+  <conditionalFormatting sqref="U8:U14">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND($B10&lt;&gt;"",U10&lt;95000)</formula>
+      <formula>AND($B8&lt;&gt;"",U8&lt;95000)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
